--- a/public/files/Data_By_Towns_Index/Burlington/Delanco Township.xlsx
+++ b/public/files/Data_By_Towns_Index/Burlington/Delanco Township.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,354 +425,239 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>Owner Name</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Owner Name</t>
+          <t>Property Location</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Property Location</t>
+          <t>Municipality</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Municipality</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>State</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Longitude</t>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>PID</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>JAIN, SHANTI R &amp; SARITA S</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KUMAR, VINODH</t>
+          <t>43 WALTON WAY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>39 TURTLE COURT</t>
+          <t>Delanco Township</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Delanco Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kumar</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>40.058675</v>
+        <v>-74.9479674</v>
       </c>
       <c r="G2" t="n">
-        <v>-74.9366615</v>
+        <v>40.04645439999999</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ChIJm_NQ409LwYkR9k26faNItl8</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PATEL, GHANSHYAM C &amp; RASIKA G</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PATEL, GHANSHYAM C &amp; RASIKA G</t>
+          <t>52 PENNINGTON COURT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>52 PENNINGTON COURT</t>
+          <t>Delanco Township</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Delanco Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Patel</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>-74.94171249999999</v>
+      </c>
+      <c r="G3" t="n">
         <v>40.0430472</v>
       </c>
-      <c r="G3" t="n">
-        <v>-74.94171249999999</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ChIJi4SrAGdLwYkR3Xbjif8OGv0</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SHARMA, VIRGINIA B</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SHAH, CHRISTINE</t>
+          <t>315 LILAC LANE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>212 WASHINGTON ST</t>
+          <t>Delanco Township</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Delanco Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shah</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>40.0461044</v>
+        <v>-74.9487706</v>
       </c>
       <c r="G4" t="n">
-        <v>-74.96056489999999</v>
+        <v>40.05328859999999</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ChIJGWTGwqBMwYkRMamjatBukGk</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KHATRI, HARI K</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SHARMA, VIRGINIA B</t>
+          <t>9 TIEMAN CIRCLE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>315 LILAC LANE</t>
+          <t>Delanco Township</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Delanco Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>40.05328859999999</v>
+        <v>-74.939167</v>
       </c>
       <c r="G5" t="n">
-        <v>-74.9487706</v>
+        <v>40.0550371</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ChIJ_5h_sp5MwYkRTotoPKmhPCk</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>4</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SHARMA, VIVEK AND REBECCA</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHARMA, VIVEK AND REBECCA</t>
+          <t>19 TIEMAN CIRCLE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19 TIEMAN CIRCLE</t>
+          <t>Delanco Township</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Delanco Township</t>
+          <t>Burlington</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>-74.93769279999999</v>
+      </c>
+      <c r="G6" t="n">
         <v>40.055412</v>
       </c>
-      <c r="G6" t="n">
-        <v>-74.93769279999999</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SONI, KETAN &amp; FALGUNI</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>614 BURLINGTON AVE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Delanco Township</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Soni</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>40.0495738</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-74.95597970000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>JAIN, DANNY C</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>33 CHARLES CIRCLE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Delanco Township</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Jain</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>40.0448668</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-74.9398157</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>JAIN, NIRLESH</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>11 TROUT TRAIL</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Delanco Township</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Jain</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>40.057196</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-74.9392012</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>JAIN, NIRLESH &amp; BHARNE, RAJ</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3 HERON LANE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Delanco Township</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Jain</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>40.0598562</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-74.93716139999999</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JAIN, SHANTI R &amp; SARITA S</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>43 WALTON WAY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Delanco Township</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Jain</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>40.04645439999999</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-74.9479674</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ChIJ1ROh8JtMwYkRS9PSlLyh0rY</t>
+        </is>
       </c>
     </row>
   </sheetData>
